--- a/artfynd/A 26085-2025 artfynd.xlsx
+++ b/artfynd/A 26085-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>84181637</v>
       </c>
       <c r="B2" t="n">
-        <v>101120</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103086</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536395.4976742762</v>
+        <v>536395</v>
       </c>
       <c r="R2" t="n">
-        <v>6909966.92737221</v>
+        <v>6909967</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -753,19 +748,9 @@
           <t>2008-08-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2008-08-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,12 +789,7 @@
         <v>84181636</v>
       </c>
       <c r="B3" t="n">
-        <v>101134</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103100</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536395.4976742762</v>
+        <v>536395</v>
       </c>
       <c r="R3" t="n">
-        <v>6909966.92737221</v>
+        <v>6909967</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,19 +859,9 @@
           <t>2008-08-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2008-08-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,12 +900,7 @@
         <v>84181633</v>
       </c>
       <c r="B4" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100668</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536404.4062839978</v>
+        <v>536404</v>
       </c>
       <c r="R4" t="n">
-        <v>6910046.992457388</v>
+        <v>6910047</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1005,19 +970,9 @@
           <t>2008-08-20</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2008-08-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1056,12 +1011,7 @@
         <v>84181605</v>
       </c>
       <c r="B5" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100761</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536262.3305341499</v>
+        <v>536262</v>
       </c>
       <c r="R5" t="n">
-        <v>6910225.374700832</v>
+        <v>6910225</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1131,19 +1081,9 @@
           <t>2008-08-20</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2008-08-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1182,12 +1122,7 @@
         <v>84181630</v>
       </c>
       <c r="B6" t="n">
-        <v>101120</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103086</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536404.4062839978</v>
+        <v>536404</v>
       </c>
       <c r="R6" t="n">
-        <v>6910046.992457388</v>
+        <v>6910047</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1257,19 +1192,9 @@
           <t>2008-08-20</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2008-08-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1308,12 +1233,7 @@
         <v>84181632</v>
       </c>
       <c r="B7" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100761</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536404.4062839978</v>
+        <v>536404</v>
       </c>
       <c r="R7" t="n">
-        <v>6910046.992457388</v>
+        <v>6910047</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1383,19 +1303,9 @@
           <t>2008-08-20</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2008-08-20</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1434,12 +1344,7 @@
         <v>84181606</v>
       </c>
       <c r="B8" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100668</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1471,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536262.3305341499</v>
+        <v>536262</v>
       </c>
       <c r="R8" t="n">
-        <v>6910225.374700832</v>
+        <v>6910225</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1509,19 +1414,9 @@
           <t>2008-08-20</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2008-08-20</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1560,12 +1455,7 @@
         <v>84181596</v>
       </c>
       <c r="B9" t="n">
-        <v>101120</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103086</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,10 +1487,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536262.3305341499</v>
+        <v>536262</v>
       </c>
       <c r="R9" t="n">
-        <v>6910225.374700832</v>
+        <v>6910225</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1635,19 +1525,9 @@
           <t>2008-08-20</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2008-08-20</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1686,12 +1566,7 @@
         <v>84181611</v>
       </c>
       <c r="B10" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98912</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,10 +1598,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536262.3305341499</v>
+        <v>536262</v>
       </c>
       <c r="R10" t="n">
-        <v>6910225.374700832</v>
+        <v>6910225</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1761,19 +1636,9 @@
           <t>2008-08-20</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2008-08-20</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1812,12 +1677,7 @@
         <v>84181638</v>
       </c>
       <c r="B11" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100761</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1849,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536395.4976742762</v>
+        <v>536395</v>
       </c>
       <c r="R11" t="n">
-        <v>6909966.92737221</v>
+        <v>6909967</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1887,19 +1747,9 @@
           <t>2008-08-20</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2008-08-20</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 26085-2025 artfynd.xlsx
+++ b/artfynd/A 26085-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84181637</v>
       </c>
       <c r="B2" t="n">
-        <v>103086</v>
+        <v>103094</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>84181636</v>
       </c>
       <c r="B3" t="n">
-        <v>103100</v>
+        <v>103108</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>84181633</v>
       </c>
       <c r="B4" t="n">
-        <v>100668</v>
+        <v>100674</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>84181605</v>
       </c>
       <c r="B5" t="n">
-        <v>100761</v>
+        <v>100768</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>84181630</v>
       </c>
       <c r="B6" t="n">
-        <v>103086</v>
+        <v>103094</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>84181632</v>
       </c>
       <c r="B7" t="n">
-        <v>100761</v>
+        <v>100768</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>84181606</v>
       </c>
       <c r="B8" t="n">
-        <v>100668</v>
+        <v>100674</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>84181596</v>
       </c>
       <c r="B9" t="n">
-        <v>103086</v>
+        <v>103094</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>84181611</v>
       </c>
       <c r="B10" t="n">
-        <v>98912</v>
+        <v>98918</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>84181638</v>
       </c>
       <c r="B11" t="n">
-        <v>100761</v>
+        <v>100768</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 26085-2025 artfynd.xlsx
+++ b/artfynd/A 26085-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84181637</v>
       </c>
       <c r="B2" t="n">
-        <v>103094</v>
+        <v>103106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>84181636</v>
       </c>
       <c r="B3" t="n">
-        <v>103108</v>
+        <v>103120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>84181633</v>
       </c>
       <c r="B4" t="n">
-        <v>100674</v>
+        <v>100679</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>84181605</v>
       </c>
       <c r="B5" t="n">
-        <v>100768</v>
+        <v>100773</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>84181630</v>
       </c>
       <c r="B6" t="n">
-        <v>103094</v>
+        <v>103106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>84181632</v>
       </c>
       <c r="B7" t="n">
-        <v>100768</v>
+        <v>100773</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>84181606</v>
       </c>
       <c r="B8" t="n">
-        <v>100674</v>
+        <v>100679</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>84181596</v>
       </c>
       <c r="B9" t="n">
-        <v>103094</v>
+        <v>103106</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>84181611</v>
       </c>
       <c r="B10" t="n">
-        <v>98918</v>
+        <v>98921</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>84181638</v>
       </c>
       <c r="B11" t="n">
-        <v>100768</v>
+        <v>100773</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 26085-2025 artfynd.xlsx
+++ b/artfynd/A 26085-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84181637</v>
       </c>
       <c r="B2" t="n">
-        <v>103106</v>
+        <v>103112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>84181636</v>
       </c>
       <c r="B3" t="n">
-        <v>103120</v>
+        <v>103126</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>84181633</v>
       </c>
       <c r="B4" t="n">
-        <v>100679</v>
+        <v>100685</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>84181605</v>
       </c>
       <c r="B5" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>84181630</v>
       </c>
       <c r="B6" t="n">
-        <v>103106</v>
+        <v>103112</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>84181632</v>
       </c>
       <c r="B7" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>84181606</v>
       </c>
       <c r="B8" t="n">
-        <v>100679</v>
+        <v>100685</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>84181596</v>
       </c>
       <c r="B9" t="n">
-        <v>103106</v>
+        <v>103112</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>84181611</v>
       </c>
       <c r="B10" t="n">
-        <v>98921</v>
+        <v>98925</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>84181638</v>
       </c>
       <c r="B11" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 26085-2025 artfynd.xlsx
+++ b/artfynd/A 26085-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84181637</v>
       </c>
       <c r="B2" t="n">
-        <v>103112</v>
+        <v>103114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>84181636</v>
       </c>
       <c r="B3" t="n">
-        <v>103126</v>
+        <v>103128</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>84181633</v>
       </c>
       <c r="B4" t="n">
-        <v>100685</v>
+        <v>100686</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>84181605</v>
       </c>
       <c r="B5" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>84181630</v>
       </c>
       <c r="B6" t="n">
-        <v>103112</v>
+        <v>103114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>84181632</v>
       </c>
       <c r="B7" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>84181606</v>
       </c>
       <c r="B8" t="n">
-        <v>100685</v>
+        <v>100686</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>84181596</v>
       </c>
       <c r="B9" t="n">
-        <v>103112</v>
+        <v>103114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>84181611</v>
       </c>
       <c r="B10" t="n">
-        <v>98925</v>
+        <v>98926</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>84181638</v>
       </c>
       <c r="B11" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 26085-2025 artfynd.xlsx
+++ b/artfynd/A 26085-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84181637</v>
       </c>
       <c r="B2" t="n">
-        <v>103114</v>
+        <v>103141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>84181636</v>
       </c>
       <c r="B3" t="n">
-        <v>103128</v>
+        <v>103155</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>84181633</v>
       </c>
       <c r="B4" t="n">
-        <v>100686</v>
+        <v>100713</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>84181605</v>
       </c>
       <c r="B5" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>84181630</v>
       </c>
       <c r="B6" t="n">
-        <v>103114</v>
+        <v>103141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>84181632</v>
       </c>
       <c r="B7" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>84181606</v>
       </c>
       <c r="B8" t="n">
-        <v>100686</v>
+        <v>100713</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>84181596</v>
       </c>
       <c r="B9" t="n">
-        <v>103114</v>
+        <v>103141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>84181611</v>
       </c>
       <c r="B10" t="n">
-        <v>98926</v>
+        <v>98953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>84181638</v>
       </c>
       <c r="B11" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 26085-2025 artfynd.xlsx
+++ b/artfynd/A 26085-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84181637</v>
       </c>
       <c r="B2" t="n">
-        <v>103141</v>
+        <v>103147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>84181636</v>
       </c>
       <c r="B3" t="n">
-        <v>103155</v>
+        <v>103161</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>84181633</v>
       </c>
       <c r="B4" t="n">
-        <v>100713</v>
+        <v>100719</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>84181605</v>
       </c>
       <c r="B5" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>84181630</v>
       </c>
       <c r="B6" t="n">
-        <v>103141</v>
+        <v>103147</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>84181632</v>
       </c>
       <c r="B7" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>84181606</v>
       </c>
       <c r="B8" t="n">
-        <v>100713</v>
+        <v>100719</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>84181596</v>
       </c>
       <c r="B9" t="n">
-        <v>103141</v>
+        <v>103147</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>84181611</v>
       </c>
       <c r="B10" t="n">
-        <v>98953</v>
+        <v>98959</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>84181638</v>
       </c>
       <c r="B11" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 26085-2025 artfynd.xlsx
+++ b/artfynd/A 26085-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84181637</v>
       </c>
       <c r="B2" t="n">
-        <v>103147</v>
+        <v>103154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>84181636</v>
       </c>
       <c r="B3" t="n">
-        <v>103161</v>
+        <v>103168</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>84181633</v>
       </c>
       <c r="B4" t="n">
-        <v>100719</v>
+        <v>100726</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>84181605</v>
       </c>
       <c r="B5" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>84181630</v>
       </c>
       <c r="B6" t="n">
-        <v>103147</v>
+        <v>103154</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>84181632</v>
       </c>
       <c r="B7" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>84181606</v>
       </c>
       <c r="B8" t="n">
-        <v>100719</v>
+        <v>100726</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>84181596</v>
       </c>
       <c r="B9" t="n">
-        <v>103147</v>
+        <v>103154</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>84181611</v>
       </c>
       <c r="B10" t="n">
-        <v>98959</v>
+        <v>98966</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>84181638</v>
       </c>
       <c r="B11" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 26085-2025 artfynd.xlsx
+++ b/artfynd/A 26085-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84181637</v>
       </c>
       <c r="B2" t="n">
-        <v>103154</v>
+        <v>103158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>84181636</v>
       </c>
       <c r="B3" t="n">
-        <v>103168</v>
+        <v>103172</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>84181633</v>
       </c>
       <c r="B4" t="n">
-        <v>100726</v>
+        <v>100730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>84181605</v>
       </c>
       <c r="B5" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>84181630</v>
       </c>
       <c r="B6" t="n">
-        <v>103154</v>
+        <v>103158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>84181632</v>
       </c>
       <c r="B7" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>84181606</v>
       </c>
       <c r="B8" t="n">
-        <v>100726</v>
+        <v>100730</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>84181596</v>
       </c>
       <c r="B9" t="n">
-        <v>103154</v>
+        <v>103158</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>84181611</v>
       </c>
       <c r="B10" t="n">
-        <v>98966</v>
+        <v>98970</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>84181638</v>
       </c>
       <c r="B11" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 26085-2025 artfynd.xlsx
+++ b/artfynd/A 26085-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84181637</v>
       </c>
       <c r="B2" t="n">
-        <v>103158</v>
+        <v>103165</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>84181636</v>
       </c>
       <c r="B3" t="n">
-        <v>103172</v>
+        <v>103179</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>84181633</v>
       </c>
       <c r="B4" t="n">
-        <v>100730</v>
+        <v>100737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>84181605</v>
       </c>
       <c r="B5" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>84181630</v>
       </c>
       <c r="B6" t="n">
-        <v>103158</v>
+        <v>103165</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>84181632</v>
       </c>
       <c r="B7" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>84181606</v>
       </c>
       <c r="B8" t="n">
-        <v>100730</v>
+        <v>100737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>84181596</v>
       </c>
       <c r="B9" t="n">
-        <v>103158</v>
+        <v>103165</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>84181611</v>
       </c>
       <c r="B10" t="n">
-        <v>98970</v>
+        <v>98977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>84181638</v>
       </c>
       <c r="B11" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 26085-2025 artfynd.xlsx
+++ b/artfynd/A 26085-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84181637</v>
       </c>
       <c r="B2" t="n">
-        <v>103168</v>
+        <v>103173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>84181636</v>
       </c>
       <c r="B3" t="n">
-        <v>103182</v>
+        <v>103187</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>84181633</v>
       </c>
       <c r="B4" t="n">
-        <v>100740</v>
+        <v>100745</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>84181605</v>
       </c>
       <c r="B5" t="n">
-        <v>100834</v>
+        <v>100839</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>84181630</v>
       </c>
       <c r="B6" t="n">
-        <v>103168</v>
+        <v>103173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>84181632</v>
       </c>
       <c r="B7" t="n">
-        <v>100834</v>
+        <v>100839</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>84181606</v>
       </c>
       <c r="B8" t="n">
-        <v>100740</v>
+        <v>100745</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>84181596</v>
       </c>
       <c r="B9" t="n">
-        <v>103168</v>
+        <v>103173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>84181611</v>
       </c>
       <c r="B10" t="n">
-        <v>98980</v>
+        <v>98985</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>84181638</v>
       </c>
       <c r="B11" t="n">
-        <v>100834</v>
+        <v>100839</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 26085-2025 artfynd.xlsx
+++ b/artfynd/A 26085-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84181637</v>
       </c>
       <c r="B2" t="n">
-        <v>103173</v>
+        <v>103181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>84181636</v>
       </c>
       <c r="B3" t="n">
-        <v>103187</v>
+        <v>103195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>84181633</v>
       </c>
       <c r="B4" t="n">
-        <v>100745</v>
+        <v>100753</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>84181605</v>
       </c>
       <c r="B5" t="n">
-        <v>100839</v>
+        <v>100847</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>84181630</v>
       </c>
       <c r="B6" t="n">
-        <v>103173</v>
+        <v>103181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>84181632</v>
       </c>
       <c r="B7" t="n">
-        <v>100839</v>
+        <v>100847</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>84181606</v>
       </c>
       <c r="B8" t="n">
-        <v>100745</v>
+        <v>100753</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>84181596</v>
       </c>
       <c r="B9" t="n">
-        <v>103173</v>
+        <v>103181</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>84181611</v>
       </c>
       <c r="B10" t="n">
-        <v>98985</v>
+        <v>98993</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>84181638</v>
       </c>
       <c r="B11" t="n">
-        <v>100839</v>
+        <v>100847</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 26085-2025 artfynd.xlsx
+++ b/artfynd/A 26085-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>84181596</v>
+        <v>84181585</v>
       </c>
       <c r="B9" t="n">
-        <v>103181</v>
+        <v>97524</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,34 +1463,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222002</v>
+        <v>221944</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Näsberget Klabbtorpsbäcken, Hls</t>
+          <t>Näsberget intill Klabbtorpsbäcken, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536262</v>
+        <v>536273</v>
       </c>
       <c r="R9" t="n">
-        <v>6910225</v>
+        <v>6910155</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1517,7 +1513,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>DIN200808201230</t>
+          <t>DIN200808201300</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1541,7 +1537,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Fuktig skog intill bäcken</t>
+          <t>Källa</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1563,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>84181611</v>
+        <v>84181596</v>
       </c>
       <c r="B10" t="n">
-        <v>98993</v>
+        <v>103181</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1574,21 +1570,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219880</v>
+        <v>222002</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1674,10 +1670,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>84181638</v>
+        <v>84181611</v>
       </c>
       <c r="B11" t="n">
-        <v>100847</v>
+        <v>98993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1685,34 +1681,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>219880</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Näsberget vid bäcken från Vandeln, Hls</t>
+          <t>Näsberget Klabbtorpsbäcken, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536395</v>
+        <v>536262</v>
       </c>
       <c r="R11" t="n">
-        <v>6909967</v>
+        <v>6910225</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1739,7 +1735,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>DIN200808201140</t>
+          <t>DIN200808201230</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1763,7 +1759,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Blockig bäckstrand i granskog</t>
+          <t>Fuktig skog intill bäcken</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1778,6 +1774,117 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr">
+        <is>
+          <t>Hälsinglands flora (2019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>84181638</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100847</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Näsberget vid bäcken från Vandeln, Hls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>536395</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6909967</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>DIN200808201140</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2008-08-20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2008-08-20</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Blockig bäckstrand i granskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Björn Wannberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anders Delin</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
         <is>
           <t>Hälsinglands flora (2019)</t>
         </is>

--- a/artfynd/A 26085-2025 artfynd.xlsx
+++ b/artfynd/A 26085-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>84181637</v>
+        <v>84181636</v>
       </c>
       <c r="B2" t="n">
-        <v>103181</v>
+        <v>103697</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222002</v>
+        <v>1665</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Skuggviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Viola selkirkii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pursh ex Goldie</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>84181636</v>
+        <v>84181640</v>
       </c>
       <c r="B3" t="n">
-        <v>103195</v>
+        <v>103697</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536395</v>
+        <v>536377</v>
       </c>
       <c r="R3" t="n">
-        <v>6909967</v>
+        <v>6909867</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -851,7 +851,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>DIN200808201140</t>
+          <t>DIN200808201120</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>84181633</v>
+        <v>84181611</v>
       </c>
       <c r="B4" t="n">
-        <v>100753</v>
+        <v>99456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,34 +908,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>219880</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Näsberget vid bäcken från Vandeln, Hls</t>
+          <t>Näsberget Klabbtorpsbäcken, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536404</v>
+        <v>536262</v>
       </c>
       <c r="R4" t="n">
-        <v>6910047</v>
+        <v>6910225</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -962,7 +962,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>DIN200808201145</t>
+          <t>DIN200808201230</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Fuktig granskog vid bäck  nedom litet fall</t>
+          <t>Fuktig skog intill bäcken</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>84181605</v>
+        <v>84181585</v>
       </c>
       <c r="B5" t="n">
-        <v>100847</v>
+        <v>97977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,34 +1019,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>221944</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Näsberget Klabbtorpsbäcken, Hls</t>
+          <t>Näsberget intill Klabbtorpsbäcken, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536262</v>
+        <v>536273</v>
       </c>
       <c r="R5" t="n">
-        <v>6910225</v>
+        <v>6910155</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1073,7 +1069,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>DIN200808201230</t>
+          <t>DIN200808201300</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1097,7 +1093,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Fuktig skog intill bäcken</t>
+          <t>Källa</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1119,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>84181630</v>
+        <v>84181596</v>
       </c>
       <c r="B6" t="n">
-        <v>103181</v>
+        <v>103683</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1150,14 +1146,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Näsberget vid bäcken från Vandeln, Hls</t>
+          <t>Näsberget Klabbtorpsbäcken, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536404</v>
+        <v>536262</v>
       </c>
       <c r="R6" t="n">
-        <v>6910047</v>
+        <v>6910225</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1184,7 +1180,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>DIN200808201145</t>
+          <t>DIN200808201230</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1208,7 +1204,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Fuktig granskog vid bäck  nedom litet fall</t>
+          <t>Fuktig skog intill bäcken</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1230,10 +1226,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>84181632</v>
+        <v>84181630</v>
       </c>
       <c r="B7" t="n">
-        <v>100847</v>
+        <v>103683</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,21 +1237,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>222002</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1341,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>84181606</v>
+        <v>84181637</v>
       </c>
       <c r="B8" t="n">
-        <v>100753</v>
+        <v>103683</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1352,16 +1348,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222771</v>
+        <v>222002</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1372,14 +1368,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Näsberget Klabbtorpsbäcken, Hls</t>
+          <t>Näsberget vid bäcken från Vandeln, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536262</v>
+        <v>536395</v>
       </c>
       <c r="R8" t="n">
-        <v>6910225</v>
+        <v>6909967</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1406,7 +1402,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>DIN200808201230</t>
+          <t>DIN200808201140</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1430,7 +1426,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Fuktig skog intill bäcken</t>
+          <t>Blockig bäckstrand i granskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1452,10 +1448,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>84181585</v>
+        <v>84181605</v>
       </c>
       <c r="B9" t="n">
-        <v>97524</v>
+        <v>101326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,30 +1459,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221944</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Näsberget intill Klabbtorpsbäcken, Hls</t>
+          <t>Näsberget Klabbtorpsbäcken, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536273</v>
+        <v>536262</v>
       </c>
       <c r="R9" t="n">
-        <v>6910155</v>
+        <v>6910225</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>DIN200808201300</t>
+          <t>DIN200808201230</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Källa</t>
+          <t>Fuktig skog intill bäcken</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1559,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>84181596</v>
+        <v>84181632</v>
       </c>
       <c r="B10" t="n">
-        <v>103181</v>
+        <v>101326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,34 +1570,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222002</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Näsberget Klabbtorpsbäcken, Hls</t>
+          <t>Näsberget vid bäcken från Vandeln, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536262</v>
+        <v>536404</v>
       </c>
       <c r="R10" t="n">
-        <v>6910225</v>
+        <v>6910047</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>DIN200808201230</t>
+          <t>DIN200808201145</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Fuktig skog intill bäcken</t>
+          <t>Fuktig granskog vid bäck  nedom litet fall</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1670,10 +1670,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>84181611</v>
+        <v>84181638</v>
       </c>
       <c r="B11" t="n">
-        <v>98993</v>
+        <v>101326</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1681,34 +1681,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219880</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Näsberget Klabbtorpsbäcken, Hls</t>
+          <t>Näsberget vid bäcken från Vandeln, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536262</v>
+        <v>536395</v>
       </c>
       <c r="R11" t="n">
-        <v>6910225</v>
+        <v>6909967</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>DIN200808201230</t>
+          <t>DIN200808201140</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Fuktig skog intill bäcken</t>
+          <t>Blockig bäckstrand i granskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1781,10 +1781,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>84181638</v>
+        <v>84181606</v>
       </c>
       <c r="B12" t="n">
-        <v>100847</v>
+        <v>101228</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1792,34 +1792,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Näsberget vid bäcken från Vandeln, Hls</t>
+          <t>Näsberget Klabbtorpsbäcken, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536395</v>
+        <v>536262</v>
       </c>
       <c r="R12" t="n">
-        <v>6909967</v>
+        <v>6910225</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>DIN200808201140</t>
+          <t>DIN200808201230</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Blockig bäckstrand i granskog</t>
+          <t>Fuktig skog intill bäcken</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1885,6 +1885,117 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr">
+        <is>
+          <t>Hälsinglands flora (2019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>84181633</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Näsberget vid bäcken från Vandeln, Hls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>536404</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6910047</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>DIN200808201145</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2008-08-20</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2008-08-20</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Fuktig granskog vid bäck  nedom litet fall</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Björn Wannberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anders Delin</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
         <is>
           <t>Hälsinglands flora (2019)</t>
         </is>

--- a/artfynd/A 26085-2025 artfynd.xlsx
+++ b/artfynd/A 26085-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Hälsinglands flora (2019)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84181636</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Hälsinglands flora (2019)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84181640</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Hälsinglands flora (2019)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84181611</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
           <t>Hälsinglands flora (2019)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84181585</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1223,6 +1248,11 @@
           <t>Hälsinglands flora (2019)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84181596</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1334,6 +1364,11 @@
           <t>Hälsinglands flora (2019)</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84181630</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1445,6 +1480,11 @@
           <t>Hälsinglands flora (2019)</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84181637</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1556,6 +1596,11 @@
           <t>Hälsinglands flora (2019)</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84181605</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1667,6 +1712,11 @@
           <t>Hälsinglands flora (2019)</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84181632</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1778,6 +1828,11 @@
           <t>Hälsinglands flora (2019)</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84181638</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1889,6 +1944,11 @@
           <t>Hälsinglands flora (2019)</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84181606</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2000,8 +2060,27 @@
           <t>Hälsinglands flora (2019)</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84181633</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>